--- a/data/trans_camb/P0902-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,61</t>
+          <t>-1,48; 2,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,53</t>
+          <t>-2,34; 1,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -1,13</t>
+          <t>-4,32; -1,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,88</t>
+          <t>-2,74; 2,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,18</t>
+          <t>-3,67; 1,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,84</t>
+          <t>-3,68; 3,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,09</t>
+          <t>-1,5; 1,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,62</t>
+          <t>-2,56; 0,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,39</t>
+          <t>-3,16; 0,45</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 204,39</t>
+          <t>-52,06; 202,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 132,57</t>
+          <t>-72,31; 121,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 99,7</t>
+          <t>-49,48; 101,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,83; 41,89</t>
+          <t>-66,48; 54,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,53; 117,28</t>
+          <t>-71,94; 117,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 84,38</t>
+          <t>-36,79; 76,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 25,88</t>
+          <t>-64,21; 21,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,55; 24,93</t>
+          <t>-80,03; 24,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,42</t>
+          <t>-1,12; 2,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,94</t>
+          <t>-0,95; 3,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,54</t>
+          <t>1,59; 8,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,86</t>
+          <t>-4,62; 0,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,02</t>
+          <t>-4,5; 1,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,86</t>
+          <t>-5,69; 0,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,06</t>
+          <t>-2,05; 1,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,46</t>
+          <t>-1,86; 1,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,44</t>
+          <t>-0,9; 3,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,82; 137,4</t>
+          <t>-37,59; 144,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 147,72</t>
+          <t>-31,93; 168,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,33; 434,85</t>
+          <t>47,33; 465,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,29; 19,93</t>
+          <t>-55,78; 14,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,27; 19,06</t>
+          <t>-54,08; 17,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 16,94</t>
+          <t>-66,0; 13,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 27,43</t>
+          <t>-39,03; 28,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 40,25</t>
+          <t>-34,91; 40,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 87,5</t>
+          <t>-19,09; 86,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,75</t>
+          <t>-1,18; 3,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,79</t>
+          <t>-2,73; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 5,07</t>
+          <t>-0,53; 4,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 6,34</t>
+          <t>-0,42; 6,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,11</t>
+          <t>-3,74; 2,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,07</t>
+          <t>-1,18; 4,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,01</t>
+          <t>0,11; 4,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,16</t>
+          <t>-2,69; 1,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,17</t>
+          <t>-0,16; 4,12</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 108,4</t>
+          <t>-21,49; 110,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,2; 55,42</t>
+          <t>-46,75; 51,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 147,1</t>
+          <t>-10,09; 132,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 89,38</t>
+          <t>-4,03; 88,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 29,77</t>
+          <t>-38,02; 30,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 75,3</t>
+          <t>-11,98; 69,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 71,15</t>
+          <t>-0,18; 74,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 20,36</t>
+          <t>-35,58; 22,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 74,07</t>
+          <t>-2,5; 74,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,35</t>
+          <t>-2,15; 4,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,72</t>
+          <t>-1,23; 5,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 7,68</t>
+          <t>-3,96; 7,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 6,47</t>
+          <t>-1,67; 6,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 3,7</t>
+          <t>-4,48; 3,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 5,66</t>
+          <t>-2,31; 5,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 4,29</t>
+          <t>-0,95; 4,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,69</t>
+          <t>-1,64; 3,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 4,93</t>
+          <t>-2,86; 5,33</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 83,75</t>
+          <t>-26,46; 84,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 107,95</t>
+          <t>-15,83; 96,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 123,25</t>
+          <t>-42,71; 133,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 59,72</t>
+          <t>-11,52; 67,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 35,19</t>
+          <t>-28,99; 37,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 52,93</t>
+          <t>-15,47; 53,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 50,75</t>
+          <t>-8,31; 52,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 43,27</t>
+          <t>-14,52; 43,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,59; 55,22</t>
+          <t>-26,18; 59,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 6,91</t>
+          <t>-3,36; 6,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 2,98</t>
+          <t>-6,25; 3,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,18</t>
+          <t>0,68; 9,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,35; 17,6</t>
+          <t>6,53; 18,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,3</t>
+          <t>2,0; 12,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 11,16</t>
+          <t>2,19; 11,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 10,81</t>
+          <t>3,43; 11,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,9</t>
+          <t>-0,42; 6,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,86; 9,11</t>
+          <t>2,84; 9,36</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 63,55</t>
+          <t>-20,54; 58,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 27,39</t>
+          <t>-38,68; 30,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4,61; 88,81</t>
+          <t>4,39; 89,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33,65; 135,41</t>
+          <t>35,92; 144,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,22; 100,01</t>
+          <t>10,45; 98,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,55; 90,84</t>
+          <t>11,56; 89,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,43; 83,67</t>
+          <t>20,55; 87,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 53,04</t>
+          <t>-2,45; 54,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17,33; 71,8</t>
+          <t>17,02; 73,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,26; 15,05</t>
+          <t>0,23; 14,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 6,04</t>
+          <t>-5,25; 6,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 5,21</t>
+          <t>-4,97; 4,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,33; 14,65</t>
+          <t>0,86; 14,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 10,55</t>
+          <t>-4,04; 10,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 0,79</t>
+          <t>-23,31; 0,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,12; 11,67</t>
+          <t>2,67; 12,1</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 5,92</t>
+          <t>-2,97; 6,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 0,67</t>
+          <t>-15,19; 0,7</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,15; 115,75</t>
+          <t>1,05; 104,62</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 45,58</t>
+          <t>-27,11; 43,74</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-23,59; 38,64</t>
+          <t>-25,46; 37,22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4,05; 55,3</t>
+          <t>2,52; 56,26</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 42,12</t>
+          <t>-12,5; 38,51</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-75,89; 3,09</t>
+          <t>-71,2; 1,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,89; 53,93</t>
+          <t>9,62; 56,28</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 28,11</t>
+          <t>-11,65; 31,0</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-59,88; 2,86</t>
+          <t>-61,1; 3,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,47; 19,48</t>
+          <t>1,36; 19,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 7,58</t>
+          <t>-8,65; 8,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 5,76</t>
+          <t>-8,9; 6,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,96; 24,63</t>
+          <t>9,36; 24,92</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,23; 18,75</t>
+          <t>3,37; 19,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,4; 18,42</t>
+          <t>4,84; 18,55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,25; 20,58</t>
+          <t>8,99; 20,28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,87; 12,29</t>
+          <t>0,78; 11,96</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,4</t>
+          <t>1,51; 11,11</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,35; 65,09</t>
+          <t>3,24; 68,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 26,6</t>
+          <t>-22,86; 28,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 19,89</t>
+          <t>-23,55; 23,56</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19,6; 66,95</t>
+          <t>20,28; 64,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,57; 49,73</t>
+          <t>6,98; 49,67</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,42; 50,88</t>
+          <t>10,15; 49,13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,46; 57,0</t>
+          <t>21,15; 57,1</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,12; 34,17</t>
+          <t>1,89; 33,78</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2,73; 31,54</t>
+          <t>3,45; 31,42</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,35</t>
+          <t>1,35; 4,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,43</t>
+          <t>-0,31; 2,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,4</t>
+          <t>0,85; 5,45</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,11</t>
+          <t>3,54; 7,2</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,93</t>
+          <t>1,48; 5,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,03; 5,58</t>
+          <t>0,12; 5,57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,33</t>
+          <t>3,03; 5,24</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,26</t>
+          <t>1,02; 3,32</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,05</t>
+          <t>1,76; 5,26</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>16,59; 58,76</t>
+          <t>15,22; 59,45</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 32,78</t>
+          <t>-3,55; 35,13</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15,05; 71,21</t>
+          <t>13,07; 72,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23,56; 52,01</t>
+          <t>23,16; 52,19</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,47; 35,94</t>
+          <t>9,78; 36,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,66; 39,64</t>
+          <t>2,46; 40,78</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,65; 48,13</t>
+          <t>24,98; 48,38</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>7,96; 30,04</t>
+          <t>8,42; 30,88</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>13,69; 45,96</t>
+          <t>15,65; 48,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0902-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-0,93</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,6</t>
+          <t>-1,29; 2,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,41</t>
+          <t>-2,23; 1,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -1,26</t>
+          <t>-3,78; -1,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,84</t>
+          <t>-2,73; 2,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,23</t>
+          <t>-3,79; 1,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,67</t>
+          <t>-2,65; 5,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,89</t>
+          <t>-1,33; 2,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,52</t>
+          <t>-2,4; 0,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,45</t>
+          <t>-2,66; 1,41</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-8,46%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-46,95%</t>
+          <t>-28,83%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 202,29</t>
+          <t>-43,17; 205,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 121,57</t>
+          <t>-73,57; 112,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,48; 101,08</t>
+          <t>-49,52; 93,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 54,13</t>
+          <t>-68,46; 51,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,94; 117,89</t>
+          <t>-54,11; 162,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 76,89</t>
+          <t>-34,4; 85,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,21; 21,15</t>
+          <t>-59,87; 32,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,03; 24,55</t>
+          <t>-70,22; 63,4</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-1,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,55</t>
+          <t>-1,06; 2,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,05</t>
+          <t>-0,99; 3,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,65</t>
+          <t>1,25; 7,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 0,73</t>
+          <t>-4,75; 0,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 1,0</t>
+          <t>-4,46; 1,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,79</t>
+          <t>-4,61; 1,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,04</t>
+          <t>-2,13; 1,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,56</t>
+          <t>-1,82; 1,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,5</t>
+          <t>-0,72; 3,44</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>176,5%</t>
+          <t>160,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-33,87%</t>
+          <t>-26,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,59; 144,67</t>
+          <t>-35,72; 158,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 168,84</t>
+          <t>-33,5; 160,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,33; 465,31</t>
+          <t>31,13; 405,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 14,28</t>
+          <t>-57,47; 16,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 17,72</t>
+          <t>-52,49; 23,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 13,51</t>
+          <t>-55,6; 20,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 28,67</t>
+          <t>-39,12; 25,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 40,76</t>
+          <t>-34,52; 41,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 86,93</t>
+          <t>-15,46; 87,93</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>1,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,89</t>
+          <t>-1,19; 4,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,67</t>
+          <t>-2,58; 1,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,93</t>
+          <t>-1,15; 4,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 6,08</t>
+          <t>-0,53; 6,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,11</t>
+          <t>-3,93; 2,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,76</t>
+          <t>-1,45; 4,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,23</t>
+          <t>-0,07; 4,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,18</t>
+          <t>-2,63; 1,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,12</t>
+          <t>-0,85; 3,45</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 110,22</t>
+          <t>-21,18; 115,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,75; 51,97</t>
+          <t>-45,77; 51,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 132,14</t>
+          <t>-21,82; 127,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 88,34</t>
+          <t>-6,04; 88,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,02; 30,36</t>
+          <t>-37,8; 34,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 69,19</t>
+          <t>-14,98; 66,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 74,08</t>
+          <t>-1,4; 74,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,58; 22,3</t>
+          <t>-33,86; 24,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 74,15</t>
+          <t>-12,31; 58,55</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>6,26</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>4,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 4,51</t>
+          <t>-2,06; 4,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,48</t>
+          <t>-0,8; 5,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 7,55</t>
+          <t>2,92; 9,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,89</t>
+          <t>-1,79; 6,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,61</t>
+          <t>-4,03; 3,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 5,59</t>
+          <t>-1,83; 5,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,5</t>
+          <t>-0,56; 4,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,6</t>
+          <t>-1,73; 3,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,33</t>
+          <t>1,51; 6,55</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 84,8</t>
+          <t>-25,63; 85,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 96,88</t>
+          <t>-10,94; 112,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,71; 133,65</t>
+          <t>32,73; 196,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 67,2</t>
+          <t>-11,81; 61,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 37,18</t>
+          <t>-26,87; 33,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 53,01</t>
+          <t>-11,79; 52,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 52,8</t>
+          <t>-5,2; 53,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 43,7</t>
+          <t>-15,54; 41,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 59,49</t>
+          <t>12,86; 78,54</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,14</t>
+          <t>6,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 6,45</t>
+          <t>-2,73; 6,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 3,22</t>
+          <t>-7,07; 2,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 9,83</t>
+          <t>-0,08; 8,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,53; 18,35</t>
+          <t>6,58; 17,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 12,76</t>
+          <t>2,69; 13,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,1</t>
+          <t>3,03; 11,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,43; 11,08</t>
+          <t>3,07; 10,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 6,96</t>
+          <t>-0,48; 6,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,36</t>
+          <t>2,79; 9,57</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 58,91</t>
+          <t>-17,36; 65,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,68; 30,11</t>
+          <t>-42,58; 24,89</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4,39; 89,7</t>
+          <t>-1,05; 80,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35,92; 144,26</t>
+          <t>34,24; 137,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,45; 98,21</t>
+          <t>15,32; 106,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,56; 89,02</t>
+          <t>15,5; 94,82</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,55; 87,38</t>
+          <t>18,05; 83,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 54,67</t>
+          <t>-2,83; 49,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17,02; 73,32</t>
+          <t>16,54; 75,76</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-10,63</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,41</t>
+          <t>-0,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,23; 14,07</t>
+          <t>0,5; 13,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 6,06</t>
+          <t>-6,0; 5,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 4,95</t>
+          <t>-5,85; 4,73</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,86; 14,23</t>
+          <t>0,65; 14,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 10,2</t>
+          <t>-4,67; 9,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 0,5</t>
+          <t>-7,0; 4,74</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,67; 12,1</t>
+          <t>2,65; 11,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,49</t>
+          <t>-3,06; 6,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 0,7</t>
+          <t>-4,65; 3,02</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>-0,95%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-36,17%</t>
+          <t>-3,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-23,12%</t>
+          <t>-3,51%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1,05; 104,62</t>
+          <t>0,38; 98,08</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 43,74</t>
+          <t>-31,33; 43,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 37,22</t>
+          <t>-29,09; 36,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2,52; 56,26</t>
+          <t>1,88; 54,6</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 38,51</t>
+          <t>-14,08; 35,78</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 1,79</t>
+          <t>-21,11; 17,64</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,62; 56,28</t>
+          <t>10,95; 56,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 31,0</t>
+          <t>-11,61; 30,42</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-61,1; 3,09</t>
+          <t>-17,55; 14,87</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>12,39</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>6,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,36; 19,67</t>
+          <t>2,18; 19,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 8,49</t>
+          <t>-9,91; 6,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 6,73</t>
+          <t>-9,69; 5,84</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9,36; 24,92</t>
+          <t>9,22; 25,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,37; 19,0</t>
+          <t>3,14; 18,94</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,84; 18,55</t>
+          <t>5,62; 18,88</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,99; 20,28</t>
+          <t>8,29; 20,12</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,78; 11,96</t>
+          <t>1,02; 12,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,11</t>
+          <t>1,29; 11,53</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-5,45%</t>
+          <t>-4,53%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,24; 68,06</t>
+          <t>4,85; 67,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 28,99</t>
+          <t>-25,44; 23,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 23,56</t>
+          <t>-24,1; 20,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20,28; 64,15</t>
+          <t>19,95; 66,27</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,98; 49,67</t>
+          <t>6,89; 50,69</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,15; 49,13</t>
+          <t>11,69; 50,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,15; 57,1</t>
+          <t>19,79; 54,67</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,89; 33,78</t>
+          <t>2,33; 34,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,45; 31,42</t>
+          <t>2,64; 31,73</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>4,73</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,5</t>
+          <t>1,44; 4,26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,66</t>
+          <t>-0,26; 2,39</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,45</t>
+          <t>2,83; 5,7</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,2</t>
+          <t>3,38; 7,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,04</t>
+          <t>1,27; 4,98</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,57</t>
+          <t>3,38; 6,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,24</t>
+          <t>2,93; 5,32</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,32</t>
+          <t>1,01; 3,37</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,26</t>
+          <t>3,61; 5,83</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>15,22; 59,45</t>
+          <t>15,92; 55,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 35,13</t>
+          <t>-2,93; 31,85</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13,07; 72,01</t>
+          <t>32,01; 76,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23,16; 52,19</t>
+          <t>21,89; 51,02</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,78; 36,37</t>
+          <t>7,98; 36,11</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,46; 40,78</t>
+          <t>21,64; 47,85</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,98; 48,38</t>
+          <t>24,18; 48,43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,42; 30,88</t>
+          <t>7,97; 30,45</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>15,65; 48,38</t>
+          <t>30,11; 53,65</t>
         </is>
       </c>
     </row>
